--- a/SOT_results/SOT_45deg.xlsx
+++ b/SOT_results/SOT_45deg.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>45° 模型数据（52点）</a:t>
+              <a:t>45° 模型数据（角度相关形状，52点）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -181,7 +181,7 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$A$2:$A$53</f>
+              <f>'Sheet1'!$A$2:$A$27</f>
             </numRef>
           </xVal>
           <yVal>
@@ -625,7 +625,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>3.703862083634493</v>
+        <v>3.526342380134457</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>3.604498389261747</v>
+        <v>3.526342380134457</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +641,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>3.597463791430061</v>
+        <v>3.526342380134457</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>3.595705141972125</v>
+        <v>3.528307906894623</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>3.598343116159009</v>
+        <v>3.541733578511137</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>3.593946492514208</v>
+        <v>3.550830045967256</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>3.592187843056272</v>
+        <v>3.548585827106368</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +681,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>3.60273973980383</v>
+        <v>3.549251458095975</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>3.593946492514208</v>
+        <v>3.548186875626934</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>3.615050286009305</v>
+        <v>3.549589879466367</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>3.607136363448631</v>
+        <v>3.551432343910026</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>3.598343116159009</v>
+        <v>3.55280471564356</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>3.603619064532798</v>
+        <v>3.551853051525675</v>
       </c>
     </row>
     <row r="15">
@@ -729,7 +729,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>3.601860415074862</v>
+        <v>3.551165397453397</v>
       </c>
     </row>
     <row r="16">
@@ -737,7 +737,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>3.613291636551369</v>
+        <v>3.551527376848587</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>3.620326234383074</v>
+        <v>3.55085740797906</v>
       </c>
     </row>
     <row r="18">
@@ -753,7 +753,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>3.613291636551369</v>
+        <v>3.549930970301326</v>
       </c>
     </row>
     <row r="19">
@@ -761,7 +761,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>3.619446909654106</v>
+        <v>3.546668684391467</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +769,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>3.623843533298927</v>
+        <v>3.537786841886478</v>
       </c>
     </row>
     <row r="21">
@@ -777,7 +777,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>3.617688260196189</v>
+        <v>3.52699286191265</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>3.624722858027895</v>
+        <v>3.515848381241267</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +793,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>3.629119481672696</v>
+        <v>3.411685606917842</v>
       </c>
     </row>
     <row r="24">
@@ -801,7 +801,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>3.64670597625194</v>
+        <v>3.480769948424751</v>
       </c>
     </row>
     <row r="25">
@@ -809,7 +809,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>3.72496587712959</v>
+        <v>3.383735311859484</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>4.053833325761496</v>
+        <v>3.356533401192288</v>
       </c>
     </row>
     <row r="27">
@@ -825,7 +825,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>4.428425660299428</v>
+        <v>3.356533401192288</v>
       </c>
     </row>
     <row r="28">
@@ -833,7 +833,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>4.285095729478572</v>
+        <v>5.059785401192287</v>
       </c>
     </row>
     <row r="29">
@@ -841,7 +841,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>4.354562383066599</v>
+        <v>5.059785401192287</v>
       </c>
     </row>
     <row r="30">
@@ -849,7 +849,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>4.374786851832728</v>
+        <v>4.938479458897321</v>
       </c>
     </row>
     <row r="31">
@@ -857,7 +857,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>4.421391062467722</v>
+        <v>4.457338101878699</v>
       </c>
     </row>
     <row r="32">
@@ -865,7 +865,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>4.41787376355187</v>
+        <v>4.479755464467104</v>
       </c>
     </row>
     <row r="33">
@@ -873,7 +873,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>4.421391062467722</v>
+        <v>4.422099034031906</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>4.439856881775935</v>
+        <v>4.414195683763694</v>
       </c>
     </row>
     <row r="35">
@@ -889,7 +889,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>4.43282228394423</v>
+        <v>4.401899796288252</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>4.445132830149704</v>
+        <v>4.400790099868041</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>4.46184</v>
+        <v>4.401576857812344</v>
       </c>
     </row>
     <row r="38">
@@ -913,7 +913,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>4.443374180691787</v>
+        <v>4.401883178871326</v>
       </c>
     </row>
     <row r="39">
@@ -921,7 +921,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>4.455684726897262</v>
+        <v>4.402459449534576</v>
       </c>
     </row>
     <row r="40">
@@ -929,7 +929,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>4.46184</v>
+        <v>4.402150058591342</v>
       </c>
     </row>
     <row r="41">
@@ -937,7 +937,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>4.500530288074341</v>
+        <v>4.401311045878155</v>
       </c>
     </row>
     <row r="42">
@@ -945,7 +945,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>4.46184</v>
+        <v>4.401011932373502</v>
       </c>
     </row>
     <row r="43">
@@ -953,7 +953,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>4.467115948373769</v>
+        <v>4.401189785450231</v>
       </c>
     </row>
     <row r="44">
@@ -961,7 +961,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>4.468874597831685</v>
+        <v>4.401461803889537</v>
       </c>
     </row>
     <row r="45">
@@ -969,7 +969,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>4.467115948373769</v>
+        <v>4.400689794736963</v>
       </c>
     </row>
     <row r="46">
@@ -977,7 +977,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>4.468874597831685</v>
+        <v>4.397179048412595</v>
       </c>
     </row>
     <row r="47">
@@ -985,7 +985,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>4.464477974186885</v>
+        <v>4.384437093408125</v>
       </c>
     </row>
     <row r="48">
@@ -993,7 +993,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>4.462719324728949</v>
+        <v>4.346324613902167</v>
       </c>
     </row>
     <row r="49">
@@ -1001,7 +1001,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>4.467995273102737</v>
+        <v>4.507677596674288</v>
       </c>
     </row>
     <row r="50">
@@ -1009,7 +1009,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>4.450408778523493</v>
+        <v>4.186534268950545</v>
       </c>
     </row>
     <row r="51">
@@ -1017,7 +1017,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>4.362476305627253</v>
+        <v>5.010746402796785</v>
       </c>
     </row>
     <row r="52">
@@ -1025,7 +1025,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>3.897313524006196</v>
+        <v>5.229594380134457</v>
       </c>
     </row>
     <row r="53">
@@ -1033,7 +1033,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>3.411046948890043</v>
+        <v>5.229594380134457</v>
       </c>
     </row>
   </sheetData>
@@ -1074,11 +1074,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1144,84 +1144,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>电阻单位</t>
+          <t>翻转幅度A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>沿用原始文件数值；原始文件未注明纵轴单位</t>
+          <t>0.851626（保持前次角度模型）</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>翻转幅度A</t>
+          <t>曲线形状</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.851626（按前次分析的平台差模型）</t>
+          <t>角度相关形状模板：0°/45°/75°实测回线归一化后按角度混合</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>中心基线</t>
+          <t>形状插值</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.036027（由已测角度基线保形插值，仅用于保持绘图尺度）</t>
+          <t>45°实测形状</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>曲线形状</t>
+          <t>纵轴单位</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>复用165°实测回线的两支路形状，按目标角度A缩放；未添加随机噪声</t>
+          <t>原始文件未注明，保留原始数值尺度</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>模型规律</t>
+          <t>实测区分</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0–90°单峰角度依赖；采用0°/45°/75°/90°实测幅度锚点的保形插值</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>实测区分</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>本文件不是该角度的实测记录；15°、30°、60°原始文件夹无实测数据，0°和45°文件也已按52点序列重新模型化</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>输入模板</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>165度.xlsx（用户上传）</t>
+          <t>本文件为模型生成数据；15°、30°、60°无原始OPJU，0°/45°为统一点数并按实测模板生成</t>
         </is>
       </c>
     </row>

--- a/SOT_results/SOT_45deg.xlsx
+++ b/SOT_results/SOT_45deg.xlsx
@@ -152,7 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>45° 模型数据（角度相关形状，52点）</a:t>
+              <a:t>45° 标准双支路SOT模型（52点）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -625,7 +625,7 @@
         <v>-0.035</v>
       </c>
       <c r="B2" t="n">
-        <v>3.526342380134457</v>
+        <v>3.610214</v>
       </c>
     </row>
     <row r="3">
@@ -633,7 +633,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B3" t="n">
-        <v>3.526342380134457</v>
+        <v>3.610214000000001</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +641,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B4" t="n">
-        <v>3.526342380134457</v>
+        <v>3.610214000000006</v>
       </c>
     </row>
     <row r="5">
@@ -649,7 +649,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B5" t="n">
-        <v>3.528307906894623</v>
+        <v>3.610214000000031</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B6" t="n">
-        <v>3.541733578511137</v>
+        <v>3.610214000000162</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>-0.021</v>
       </c>
       <c r="B7" t="n">
-        <v>3.550830045967256</v>
+        <v>3.610214000000838</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B8" t="n">
-        <v>3.548585827106368</v>
+        <v>3.610214000004351</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +681,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B9" t="n">
-        <v>3.549251458095975</v>
+        <v>3.610214000022589</v>
       </c>
     </row>
     <row r="10">
@@ -689,7 +689,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B10" t="n">
-        <v>3.548186875626934</v>
+        <v>3.610214000117276</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B11" t="n">
-        <v>3.549589879466367</v>
+        <v>3.610214000608861</v>
       </c>
     </row>
     <row r="12">
@@ -705,7 +705,7 @@
         <v>-0.007</v>
       </c>
       <c r="B12" t="n">
-        <v>3.551432343910026</v>
+        <v>3.610214003161015</v>
       </c>
     </row>
     <row r="13">
@@ -713,7 +713,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B13" t="n">
-        <v>3.55280471564356</v>
+        <v>3.610214016411005</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B14" t="n">
-        <v>3.551853051525675</v>
+        <v>3.610214085200803</v>
       </c>
     </row>
     <row r="15">
@@ -729,7 +729,7 @@
         <v>0.0014</v>
       </c>
       <c r="B15" t="n">
-        <v>3.551165397453397</v>
+        <v>3.610214442335776</v>
       </c>
     </row>
     <row r="16">
@@ -737,7 +737,7 @@
         <v>0.0042</v>
       </c>
       <c r="B16" t="n">
-        <v>3.551527376848587</v>
+        <v>3.610216296464196</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         <v>0.007</v>
       </c>
       <c r="B17" t="n">
-        <v>3.55085740797906</v>
+        <v>3.610225922390113</v>
       </c>
     </row>
     <row r="18">
@@ -753,7 +753,7 @@
         <v>0.0098</v>
       </c>
       <c r="B18" t="n">
-        <v>3.549930970301326</v>
+        <v>3.610275893693837</v>
       </c>
     </row>
     <row r="19">
@@ -761,7 +761,7 @@
         <v>0.0126</v>
       </c>
       <c r="B19" t="n">
-        <v>3.546668684391467</v>
+        <v>3.610535234866895</v>
       </c>
     </row>
     <row r="20">
@@ -769,7 +769,7 @@
         <v>0.0154</v>
       </c>
       <c r="B20" t="n">
-        <v>3.537786841886478</v>
+        <v>3.61187911836197</v>
       </c>
     </row>
     <row r="21">
@@ -777,7 +777,7 @@
         <v>0.0182</v>
       </c>
       <c r="B21" t="n">
-        <v>3.52699286191265</v>
+        <v>3.618788500603038</v>
       </c>
     </row>
     <row r="22">
@@ -785,7 +785,7 @@
         <v>0.021</v>
       </c>
       <c r="B22" t="n">
-        <v>3.515848381241267</v>
+        <v>3.652927469688595</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +793,7 @@
         <v>0.0238</v>
       </c>
       <c r="B23" t="n">
-        <v>3.411685606917842</v>
+        <v>3.793447015792268</v>
       </c>
     </row>
     <row r="24">
@@ -801,7 +801,7 @@
         <v>0.0266</v>
       </c>
       <c r="B24" t="n">
-        <v>3.480769948424751</v>
+        <v>4.110400030319937</v>
       </c>
     </row>
     <row r="25">
@@ -809,7 +809,7 @@
         <v>0.0294</v>
       </c>
       <c r="B25" t="n">
-        <v>3.383735311859484</v>
+        <v>4.360323692329992</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         <v>0.0322</v>
       </c>
       <c r="B26" t="n">
-        <v>3.356533401192288</v>
+        <v>4.440204079390156</v>
       </c>
     </row>
     <row r="27">
@@ -825,7 +825,7 @@
         <v>0.035</v>
       </c>
       <c r="B27" t="n">
-        <v>3.356533401192288</v>
+        <v>4.457585312412417</v>
       </c>
     </row>
     <row r="28">
@@ -833,7 +833,7 @@
         <v>0.035</v>
       </c>
       <c r="B28" t="n">
-        <v>5.059785401192287</v>
+        <v>4.46184</v>
       </c>
     </row>
     <row r="29">
@@ -841,7 +841,7 @@
         <v>0.0322</v>
       </c>
       <c r="B29" t="n">
-        <v>5.059785401192287</v>
+        <v>4.461839999999999</v>
       </c>
     </row>
     <row r="30">
@@ -849,7 +849,7 @@
         <v>0.0294</v>
       </c>
       <c r="B30" t="n">
-        <v>4.938479458897321</v>
+        <v>4.461839999999994</v>
       </c>
     </row>
     <row r="31">
@@ -857,7 +857,7 @@
         <v>0.0266</v>
       </c>
       <c r="B31" t="n">
-        <v>4.457338101878699</v>
+        <v>4.461839999999969</v>
       </c>
     </row>
     <row r="32">
@@ -865,7 +865,7 @@
         <v>0.0238</v>
       </c>
       <c r="B32" t="n">
-        <v>4.479755464467104</v>
+        <v>4.461839999999839</v>
       </c>
     </row>
     <row r="33">
@@ -873,7 +873,7 @@
         <v>0.021</v>
       </c>
       <c r="B33" t="n">
-        <v>4.422099034031906</v>
+        <v>4.461839999999162</v>
       </c>
     </row>
     <row r="34">
@@ -881,7 +881,7 @@
         <v>0.0182</v>
       </c>
       <c r="B34" t="n">
-        <v>4.414195683763694</v>
+        <v>4.461839999995649</v>
       </c>
     </row>
     <row r="35">
@@ -889,7 +889,7 @@
         <v>0.0154</v>
       </c>
       <c r="B35" t="n">
-        <v>4.401899796288252</v>
+        <v>4.461839999977411</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.0126</v>
       </c>
       <c r="B36" t="n">
-        <v>4.400790099868041</v>
+        <v>4.461839999882724</v>
       </c>
     </row>
     <row r="37">
@@ -905,7 +905,7 @@
         <v>0.0098</v>
       </c>
       <c r="B37" t="n">
-        <v>4.401576857812344</v>
+        <v>4.461839999391139</v>
       </c>
     </row>
     <row r="38">
@@ -913,7 +913,7 @@
         <v>0.007</v>
       </c>
       <c r="B38" t="n">
-        <v>4.401883178871326</v>
+        <v>4.461839996838984</v>
       </c>
     </row>
     <row r="39">
@@ -921,7 +921,7 @@
         <v>0.0042</v>
       </c>
       <c r="B39" t="n">
-        <v>4.402459449534576</v>
+        <v>4.461839983588995</v>
       </c>
     </row>
     <row r="40">
@@ -929,7 +929,7 @@
         <v>0.0014</v>
       </c>
       <c r="B40" t="n">
-        <v>4.402150058591342</v>
+        <v>4.461839914799197</v>
       </c>
     </row>
     <row r="41">
@@ -937,7 +937,7 @@
         <v>-0.0014</v>
       </c>
       <c r="B41" t="n">
-        <v>4.401311045878155</v>
+        <v>4.461839557664224</v>
       </c>
     </row>
     <row r="42">
@@ -945,7 +945,7 @@
         <v>-0.0042</v>
       </c>
       <c r="B42" t="n">
-        <v>4.401011932373502</v>
+        <v>4.461837703535804</v>
       </c>
     </row>
     <row r="43">
@@ -953,7 +953,7 @@
         <v>-0.007</v>
       </c>
       <c r="B43" t="n">
-        <v>4.401189785450231</v>
+        <v>4.461828077609887</v>
       </c>
     </row>
     <row r="44">
@@ -961,7 +961,7 @@
         <v>-0.0098</v>
       </c>
       <c r="B44" t="n">
-        <v>4.401461803889537</v>
+        <v>4.461778106306164</v>
       </c>
     </row>
     <row r="45">
@@ -969,7 +969,7 @@
         <v>-0.0126</v>
       </c>
       <c r="B45" t="n">
-        <v>4.400689794736963</v>
+        <v>4.461518765133105</v>
       </c>
     </row>
     <row r="46">
@@ -977,7 +977,7 @@
         <v>-0.0154</v>
       </c>
       <c r="B46" t="n">
-        <v>4.397179048412595</v>
+        <v>4.46017488163803</v>
       </c>
     </row>
     <row r="47">
@@ -985,7 +985,7 @@
         <v>-0.0182</v>
       </c>
       <c r="B47" t="n">
-        <v>4.384437093408125</v>
+        <v>4.453265499396961</v>
       </c>
     </row>
     <row r="48">
@@ -993,7 +993,7 @@
         <v>-0.021</v>
       </c>
       <c r="B48" t="n">
-        <v>4.346324613902167</v>
+        <v>4.419126530311405</v>
       </c>
     </row>
     <row r="49">
@@ -1001,7 +1001,7 @@
         <v>-0.0238</v>
       </c>
       <c r="B49" t="n">
-        <v>4.507677596674288</v>
+        <v>4.278606984207732</v>
       </c>
     </row>
     <row r="50">
@@ -1009,7 +1009,7 @@
         <v>-0.0266</v>
       </c>
       <c r="B50" t="n">
-        <v>4.186534268950545</v>
+        <v>3.961653969680063</v>
       </c>
     </row>
     <row r="51">
@@ -1017,7 +1017,7 @@
         <v>-0.0294</v>
       </c>
       <c r="B51" t="n">
-        <v>5.010746402796785</v>
+        <v>3.711730307670008</v>
       </c>
     </row>
     <row r="52">
@@ -1025,7 +1025,7 @@
         <v>-0.0322</v>
       </c>
       <c r="B52" t="n">
-        <v>5.229594380134457</v>
+        <v>3.631849920609843</v>
       </c>
     </row>
     <row r="53">
@@ -1033,7 +1033,7 @@
         <v>-0.035</v>
       </c>
       <c r="B53" t="n">
-        <v>5.229594380134457</v>
+        <v>3.614468687587583</v>
       </c>
     </row>
   </sheetData>
@@ -1074,11 +1074,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>模型生成（非实测）</t>
+          <t>标准双支路模型生成（非实测）</t>
         </is>
       </c>
     </row>
@@ -1149,55 +1149,67 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.851626（保持前次角度模型）</t>
+          <t>0.851626</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>曲线形状</t>
+          <t>开关阈值Ic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>角度相关形状模板：0°/45°/75°实测回线归一化后按角度混合</t>
+          <t>±0.02600000 A（平滑角度模型）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>形状插值</t>
+          <t>开关宽度</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>45°实测形状</t>
+          <t>0.00170000 A（窄开关区）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>纵轴单位</t>
+          <t>曲线结构</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>原始文件未注明，保留原始数值尺度</t>
+          <t>支路1在+Ic由低平台翻到高平台；支路2在−Ic由高平台翻到低平台</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>噪声处理</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>未添加随机噪声；未使用原始回线端点噪声</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>实测区分</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>本文件为模型生成数据；15°、30°、60°无原始OPJU，0°/45°为统一点数并按实测模板生成</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>本文件是模型预测/标准化数据，不是该角度的原始实测记录</t>
         </is>
       </c>
     </row>
